--- a/My project/Assets/StreamingAssets/Stage01.xlsx
+++ b/My project/Assets/StreamingAssets/Stage01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Desktop\新しいフォルダー (2)\My project\Assets\Scenes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\riki1\Desktop\新しいフォルダー\My project\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECC5378E-518C-44B3-A617-44ECD2BBE1B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8840C860-6F59-4CFE-AAE1-038698AD12B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{7919BEF3-04A8-4746-BFAC-68B3B860663E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7919BEF3-04A8-4746-BFAC-68B3B860663E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,9 +30,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -418,9 +415,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A7F56FC-8427-4BBB-B9AF-5D530DB68D84}">
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="3.5625" defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
+  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1">
         <v>1</v>
       </c>
@@ -458,7 +455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.7">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -466,7 +463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.7">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -474,7 +471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.7">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -482,7 +479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.7">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1</v>
       </c>
@@ -490,15 +487,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.7">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>1</v>
       </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
       <c r="L6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.7">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>1</v>
       </c>

--- a/My project/Assets/StreamingAssets/Stage01.xlsx
+++ b/My project/Assets/StreamingAssets/Stage01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\riki1\Desktop\新しいフォルダー\My project\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Desktop\新しいフォルダー\My project\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8840C860-6F59-4CFE-AAE1-038698AD12B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E883D96E-EBCD-42FB-B8A9-17231DC8C917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7919BEF3-04A8-4746-BFAC-68B3B860663E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{7919BEF3-04A8-4746-BFAC-68B3B860663E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -414,10 +417,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A7F56FC-8427-4BBB-B9AF-5D530DB68D84}">
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:Q12"/>
+  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.7">
       <c r="A1">
         <v>1</v>
       </c>
@@ -454,85 +457,155 @@
       <c r="L1">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M1">
+        <v>1</v>
+      </c>
+      <c r="N1">
+        <v>1</v>
+      </c>
+      <c r="O1">
+        <v>1</v>
+      </c>
+      <c r="P1">
+        <v>1</v>
+      </c>
+      <c r="Q1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.7">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="Q2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.7">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="Q3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.7">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="Q4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.7">
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="Q5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.7">
       <c r="A6">
         <v>1</v>
       </c>
-      <c r="B6">
+      <c r="Q6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
         <v>2</v>
       </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
+      <c r="Q11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
         <v>1</v>
       </c>
     </row>

--- a/My project/Assets/StreamingAssets/Stage01.xlsx
+++ b/My project/Assets/StreamingAssets/Stage01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Desktop\新しいフォルダー\My project\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E883D96E-EBCD-42FB-B8A9-17231DC8C917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7276B69-CD96-4C4D-8FC2-5D0243EF282E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{7919BEF3-04A8-4746-BFAC-68B3B860663E}"/>
   </bookViews>
@@ -477,6 +477,9 @@
       <c r="A2">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
       <c r="Q2">
         <v>1</v>
       </c>
@@ -485,6 +488,24 @@
       <c r="A3">
         <v>1</v>
       </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>4</v>
+      </c>
       <c r="Q3">
         <v>1</v>
       </c>
@@ -493,6 +514,15 @@
       <c r="A4">
         <v>1</v>
       </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
       <c r="Q4">
         <v>1</v>
       </c>
@@ -501,6 +531,21 @@
       <c r="A5">
         <v>1</v>
       </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
       <c r="Q5">
         <v>1</v>
       </c>
@@ -509,6 +554,9 @@
       <c r="A6">
         <v>1</v>
       </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
       <c r="Q6">
         <v>1</v>
       </c>
@@ -517,6 +565,24 @@
       <c r="A7">
         <v>1</v>
       </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
       <c r="Q7">
         <v>1</v>
       </c>
@@ -525,6 +591,12 @@
       <c r="A8">
         <v>1</v>
       </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
       <c r="Q8">
         <v>1</v>
       </c>
@@ -533,6 +605,15 @@
       <c r="A9">
         <v>1</v>
       </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
       <c r="Q9">
         <v>1</v>
       </c>
@@ -541,6 +622,30 @@
       <c r="A10">
         <v>1</v>
       </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>4</v>
+      </c>
       <c r="Q10">
         <v>1</v>
       </c>
@@ -549,8 +654,8 @@
       <c r="A11">
         <v>1</v>
       </c>
-      <c r="B11">
-        <v>2</v>
+      <c r="P11">
+        <v>3</v>
       </c>
       <c r="Q11">
         <v>1</v>
